--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Função EXATO.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/Função EXATO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C29FAB4-ADF8-47B1-826F-AE307A8FBE8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7C3EC5-2610-4311-95A0-B074F3328D4F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
